--- a/Config/matter.xlsx
+++ b/Config/matter.xlsx
@@ -31,7 +31,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
-    <t>matterID</t>
+    <t>ID</t>
   </si>
   <si>
     <t>name</t>
